--- a/Chronologie2026.xlsx
+++ b/Chronologie2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecomuseum.sharepoint.com/sites/RechercheetConservation/Documents partages/SUIVI/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="508" documentId="8_{3EF83A5C-6DCC-47B5-8D1E-56C601A76992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BDE492A-8831-476F-89CF-7CCB8D0432C1}"/>
+  <xr:revisionPtr revIDLastSave="516" documentId="8_{3EF83A5C-6DCC-47B5-8D1E-56C601A76992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF53B07A-206D-4365-98F1-9BA80C7965C8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{50DE335B-1AC2-40BA-BF47-5A92BF0C7D95}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="48">
   <si>
     <t>Espèce</t>
   </si>
@@ -676,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD6CD39-F739-43EC-8F19-3C87262D3302}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1159,6 +1159,58 @@
         <v>47</v>
       </c>
     </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2">
+        <v>141</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2">
+        <v>141</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
@@ -1169,6 +1221,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7a604ce4-e110-496b-b514-05cf52b55d58">
@@ -1177,15 +1238,6 @@
     <TaxCatchAll xmlns="52f59610-9d4b-4eee-b073-9157bca3f72d" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1402,20 +1454,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3851125A-FB49-4FC6-8FFA-1DA756BF2BAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72B39488-16AA-4F96-A62E-293388E6B9F1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="7a604ce4-e110-496b-b514-05cf52b55d58"/>
     <ds:schemaRef ds:uri="52f59610-9d4b-4eee-b073-9157bca3f72d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3851125A-FB49-4FC6-8FFA-1DA756BF2BAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Chronologie2026.xlsx
+++ b/Chronologie2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecomuseum.sharepoint.com/sites/RechercheetConservation/Documents partages/SUIVI/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="516" documentId="8_{3EF83A5C-6DCC-47B5-8D1E-56C601A76992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF53B07A-206D-4365-98F1-9BA80C7965C8}"/>
+  <xr:revisionPtr revIDLastSave="518" documentId="8_{3EF83A5C-6DCC-47B5-8D1E-56C601A76992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241CD875-F02C-498A-8E70-853FEACB19F9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{50DE335B-1AC2-40BA-BF47-5A92BF0C7D95}"/>
+    <workbookView xWindow="1740" yWindow="1875" windowWidth="24420" windowHeight="13950" xr2:uid="{50DE335B-1AC2-40BA-BF47-5A92BF0C7D95}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -357,6 +357,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1127,7 +1131,7 @@
         <v>34</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>47</v>
@@ -1153,7 +1157,7 @@
         <v>34</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>47</v>
@@ -1221,26 +1225,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7a604ce4-e110-496b-b514-05cf52b55d58">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="52f59610-9d4b-4eee-b073-9157bca3f72d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001EC185F503A6BF4496F48AD665D177EC" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="72383f23a55611236396421b4e508648">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7a604ce4-e110-496b-b514-05cf52b55d58" xmlns:ns3="52f59610-9d4b-4eee-b073-9157bca3f72d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3226e9736d8ed1e2c49577e6652bfdc6" ns2:_="" ns3:_="">
     <xsd:import namespace="7a604ce4-e110-496b-b514-05cf52b55d58"/>
@@ -1453,10 +1437,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7a604ce4-e110-496b-b514-05cf52b55d58">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="52f59610-9d4b-4eee-b073-9157bca3f72d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3851125A-FB49-4FC6-8FFA-1DA756BF2BAF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C28474C2-380E-4D59-B081-79F8DCF34163}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7a604ce4-e110-496b-b514-05cf52b55d58"/>
+    <ds:schemaRef ds:uri="52f59610-9d4b-4eee-b073-9157bca3f72d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1473,20 +1488,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C28474C2-380E-4D59-B081-79F8DCF34163}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3851125A-FB49-4FC6-8FFA-1DA756BF2BAF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7a604ce4-e110-496b-b514-05cf52b55d58"/>
-    <ds:schemaRef ds:uri="52f59610-9d4b-4eee-b073-9157bca3f72d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>